--- a/satisfaction_surveys/018_lash_fill_interval_preference_survey--satisfaction_surveys.xlsx
+++ b/satisfaction_surveys/018_lash_fill_interval_preference_survey--satisfaction_surveys.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -709,7 +709,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Comments</t>
+          <t>Lash Frequency Comments</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
@@ -870,7 +870,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>How satisfied would you be with this frequency?</t>
+          <t>Lash Salon Frequency Satisfaction</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
@@ -888,12 +888,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>lash_influence_salon</t>
+          <t>lash_influence_salon_2</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>What factors influence your desire for this frequency?</t>
+          <t>Lash Influence Salon 2</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
@@ -1003,7 +1003,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>lash_influence_minimalist</t>
+          <t>lash_influence_minimalist_2</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1031,7 +1031,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>How satisfied are you with visiting for lash fills?</t>
+          <t>Minimalist Frequency Satisfaction</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
@@ -1054,7 +1054,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>What influences your satisfaction with visiting for lash fills?</t>
+          <t>Lash Frequency Minimalist Influence</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
@@ -1959,7 +1959,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>lash_influence_salon_choices</t>
+          <t>lash_influence_salon_2_choices</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -1976,7 +1976,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>lash_influence_salon_choices</t>
+          <t>lash_influence_salon_2_choices</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -1993,7 +1993,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>lash_influence_salon_choices</t>
+          <t>lash_influence_salon_2_choices</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -2010,7 +2010,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>lash_influence_salon_choices</t>
+          <t>lash_influence_salon_2_choices</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -2248,7 +2248,7 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>lash_influence_minimalist_choices</t>
+          <t>lash_influence_minimalist_2_choices</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -2265,7 +2265,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>lash_influence_minimalist_choices</t>
+          <t>lash_influence_minimalist_2_choices</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -2282,7 +2282,7 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>lash_influence_minimalist_choices</t>
+          <t>lash_influence_minimalist_2_choices</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -2299,7 +2299,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>lash_influence_minimalist_choices</t>
+          <t>lash_influence_minimalist_2_choices</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
